--- a/api/clv2/xlsx/en/UNSDG-Indicators.xlsx
+++ b/api/clv2/xlsx/en/UNSDG-Indicators.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="652">
   <si>
     <t>code</t>
   </si>
@@ -106,19 +106,28 @@
     <t>Proportion of local governments that adopt and implement local disaster risk reduction strategies in line with national disaster risk reduction strategies</t>
   </si>
   <si>
+    <t>1.a.1</t>
+  </si>
+  <si>
+    <t>Total official development assistance grants from all donors that focus on poverty reduction as a share of the recipient country’s gross national income</t>
+  </si>
+  <si>
+    <t>1.a</t>
+  </si>
+  <si>
     <t>1.a.2</t>
   </si>
   <si>
     <t>Proportion of total government spending on essential services (education, health and social protection)</t>
   </si>
   <si>
-    <t>1.a</t>
-  </si>
-  <si>
-    <t>1.a.1</t>
-  </si>
-  <si>
-    <t>Total official development assistance grants from all donors that focus on poverty reduction as a share of the recipient country’s gross national income</t>
+    <t>1.b.1</t>
+  </si>
+  <si>
+    <t>Pro-poor public social spending</t>
+  </si>
+  <si>
+    <t>1.b</t>
   </si>
   <si>
     <t>2.1.1</t>
@@ -172,6 +181,15 @@
     <t>Average income of small-scale food producers, by sex and indigenous status</t>
   </si>
   <si>
+    <t>2.4.1</t>
+  </si>
+  <si>
+    <t>Proportion of agricultural area under productive and sustainable agriculture</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
     <t>2.5.1</t>
   </si>
   <si>
@@ -271,18 +289,18 @@
     <t>Malaria incidence per 1,000 population</t>
   </si>
   <si>
+    <t>3.3.4</t>
+  </si>
+  <si>
+    <t>Hepatitis B incidence per 100,000 population</t>
+  </si>
+  <si>
     <t>3.3.5</t>
   </si>
   <si>
     <t>Number of people requiring interventions against neglected tropical diseases</t>
   </si>
   <si>
-    <t>3.3.4</t>
-  </si>
-  <si>
-    <t>Hepatitis B incidence per 100,000 population</t>
-  </si>
-  <si>
     <t>3.4.1</t>
   </si>
   <si>
@@ -298,21 +316,21 @@
     <t>Suicide mortality rate</t>
   </si>
   <si>
+    <t>3.5.1</t>
+  </si>
+  <si>
+    <t>Coverage of treatment interventions (pharmacological, psychosocial and rehabilitation and aftercare services) for substance use disorders</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
     <t>3.5.2</t>
   </si>
   <si>
     <t>Alcohol per capita consumption (aged 15 years and older) within a calendar year in litres of pure alcohol</t>
   </si>
   <si>
-    <t>3.5</t>
-  </si>
-  <si>
-    <t>3.5.1</t>
-  </si>
-  <si>
-    <t>Coverage of treatment interventions (pharmacological, psychosocial and rehabilitation and aftercare services) for substance use disorders</t>
-  </si>
-  <si>
     <t>3.6.1</t>
   </si>
   <si>
@@ -337,21 +355,21 @@
     <t>Adolescent birth rate (aged 10-14 years; aged 15-19 years) per 1,000 women in that age group</t>
   </si>
   <si>
+    <t>3.8.1</t>
+  </si>
+  <si>
+    <t>Coverage of essential health services</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
     <t>3.8.2</t>
   </si>
   <si>
     <t>Proportion of population with large household expenditures on health as a share of total household expenditure or income</t>
   </si>
   <si>
-    <t>3.8</t>
-  </si>
-  <si>
-    <t>3.8.1</t>
-  </si>
-  <si>
-    <t>Coverage of essential health services</t>
-  </si>
-  <si>
     <t>3.9.1</t>
   </si>
   <si>
@@ -382,21 +400,21 @@
     <t>3.a</t>
   </si>
   <si>
+    <t>3.b.1</t>
+  </si>
+  <si>
+    <t>Proportion of the target population covered by all vaccines included in their national programme</t>
+  </si>
+  <si>
+    <t>3.b</t>
+  </si>
+  <si>
     <t>3.b.2</t>
   </si>
   <si>
     <t>Total net official development assistance to medical research and basic health sectors</t>
   </si>
   <si>
-    <t>3.b</t>
-  </si>
-  <si>
-    <t>3.b.1</t>
-  </si>
-  <si>
-    <t>Proportion of the target population covered by all vaccines included in their national programme</t>
-  </si>
-  <si>
     <t>3.b.3</t>
   </si>
   <si>
@@ -493,6 +511,15 @@
     <t>4.6</t>
   </si>
   <si>
+    <t>4.7.1</t>
+  </si>
+  <si>
+    <t>Extent to which (i) global citizenship education and (ii) education for sustainable development are mainstreamed in (a) national education policies; (b) curricula; (c) teacher education; and (d) student assessment</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
     <t>4.a.1</t>
   </si>
   <si>
@@ -538,6 +565,12 @@
     <t>5.2</t>
   </si>
   <si>
+    <t>5.2.2</t>
+  </si>
+  <si>
+    <t>Proportion of women and girls aged 15 years and older subjected to sexual violence by persons other than an intimate partner in the previous 12 months, by age and place of occurrence</t>
+  </si>
+  <si>
     <t>5.3.1</t>
   </si>
   <si>
@@ -643,19 +676,28 @@
     <t>6.2</t>
   </si>
   <si>
+    <t>6.3.1</t>
+  </si>
+  <si>
+    <t>Proportion of domestic and industrial wastewater flows safely treated</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
     <t>6.3.2</t>
   </si>
   <si>
     <t>Proportion of bodies of water with good ambient water quality</t>
   </si>
   <si>
-    <t>6.3</t>
-  </si>
-  <si>
-    <t>6.3.1</t>
-  </si>
-  <si>
-    <t>Proportion of domestic and industrial wastewater flows safely treated</t>
+    <t>6.4.1</t>
+  </si>
+  <si>
+    <t>Change in water-use efficiency over time</t>
+  </si>
+  <si>
+    <t>6.4</t>
   </si>
   <si>
     <t>6.4.2</t>
@@ -664,15 +706,6 @@
     <t>Level of water stress: freshwater withdrawal as a proportion of available freshwater resources</t>
   </si>
   <si>
-    <t>6.4</t>
-  </si>
-  <si>
-    <t>6.4.1</t>
-  </si>
-  <si>
-    <t>Change in water-use efficiency over time</t>
-  </si>
-  <si>
     <t>6.5.1</t>
   </si>
   <si>
@@ -766,6 +799,15 @@
     <t>7.b</t>
   </si>
   <si>
+    <t>8.1.1</t>
+  </si>
+  <si>
+    <t>Annual growth rate of real GDP per capita</t>
+  </si>
+  <si>
+    <t>8.1</t>
+  </si>
+  <si>
     <t>8.2.1</t>
   </si>
   <si>
@@ -832,15 +874,6 @@
     <t>8.7</t>
   </si>
   <si>
-    <t>8.1.1</t>
-  </si>
-  <si>
-    <t>Annual growth rate of real GDP per capita</t>
-  </si>
-  <si>
-    <t>8.1</t>
-  </si>
-  <si>
     <t>8.8.1</t>
   </si>
   <si>
@@ -898,21 +931,21 @@
     <t>8.b</t>
   </si>
   <si>
+    <t>9.1.1</t>
+  </si>
+  <si>
+    <t>Proportion of the rural population who live within 2 km of an all-season road</t>
+  </si>
+  <si>
+    <t>9.1</t>
+  </si>
+  <si>
     <t>9.1.2</t>
   </si>
   <si>
     <t>Passenger and freight volumes, by mode of transport</t>
   </si>
   <si>
-    <t>9.1</t>
-  </si>
-  <si>
-    <t>9.1.1</t>
-  </si>
-  <si>
-    <t>Proportion of the rural population who live within 2 km of an all-season road</t>
-  </si>
-  <si>
     <t>9.2.1</t>
   </si>
   <si>
@@ -1054,15 +1087,21 @@
     <t>10.6</t>
   </si>
   <si>
+    <t>10.7.1</t>
+  </si>
+  <si>
+    <t>Recruitment cost borne by employee as a proportion of monthly income earned in country of destination</t>
+  </si>
+  <si>
+    <t>10.7</t>
+  </si>
+  <si>
     <t>10.7.2</t>
   </si>
   <si>
     <t>Number of countries with migration policies that facilitate orderly, safe, regular and responsible migration and mobility of people</t>
   </si>
   <si>
-    <t>10.7</t>
-  </si>
-  <si>
     <t>10.7.3</t>
   </si>
   <si>
@@ -1111,6 +1150,39 @@
     <t>11.1</t>
   </si>
   <si>
+    <t>11.2.1</t>
+  </si>
+  <si>
+    <t>Proportion of population that has convenient access to public transport, by sex, age and persons with disabilities</t>
+  </si>
+  <si>
+    <t>11.2</t>
+  </si>
+  <si>
+    <t>11.3.1</t>
+  </si>
+  <si>
+    <t>Ratio of land consumption rate to population growth rate</t>
+  </si>
+  <si>
+    <t>11.3</t>
+  </si>
+  <si>
+    <t>11.3.2</t>
+  </si>
+  <si>
+    <t>Proportion of cities with a direct participation structure of civil society in urban planning and management that operate regularly and democratically</t>
+  </si>
+  <si>
+    <t>11.4.1</t>
+  </si>
+  <si>
+    <t>Total per capita expenditure on the preservation, protection and conservation of all cultural and natural heritage, by source of funding (public, private), type of heritage (cultural, natural) and level of government (national, regional, and local/municipal)</t>
+  </si>
+  <si>
+    <t>11.4</t>
+  </si>
+  <si>
     <t>11.5.1</t>
   </si>
   <si>
@@ -1138,6 +1210,21 @@
     <t>Annual mean levels of fine particulate matter (e.g. PM2.5 and PM10) in cities (population weighted)</t>
   </si>
   <si>
+    <t>11.7.1</t>
+  </si>
+  <si>
+    <t>Average share of the built-up area of cities that is open space for public use for all, by sex, age and persons with disabilities</t>
+  </si>
+  <si>
+    <t>11.7</t>
+  </si>
+  <si>
+    <t>11.7.2</t>
+  </si>
+  <si>
+    <t>Proportion of persons victim of physical or sexual harassment, by sex, age, disability status and place of occurrence, in the previous 12 months</t>
+  </si>
+  <si>
     <t>11.a.1</t>
   </si>
   <si>
@@ -1225,6 +1312,12 @@
     <t>12.7</t>
   </si>
   <si>
+    <t>12.8.1</t>
+  </si>
+  <si>
+    <t>12.8</t>
+  </si>
+  <si>
     <t>12.a.1</t>
   </si>
   <si>
@@ -1261,19 +1354,25 @@
     <t>13.1.3</t>
   </si>
   <si>
+    <t>13.2.1</t>
+  </si>
+  <si>
+    <t>Number of countries with nationally determined contributions, long-term strategies, national adaptation plans and adaptation communications, as reported to the secretariat of the United Nations Framework Convention on Climate Change</t>
+  </si>
+  <si>
+    <t>13.2</t>
+  </si>
+  <si>
     <t>13.2.2</t>
   </si>
   <si>
     <t>Total greenhouse gas emissions per year</t>
   </si>
   <si>
-    <t>13.2</t>
-  </si>
-  <si>
-    <t>13.2.1</t>
-  </si>
-  <si>
-    <t>Number of countries with nationally determined contributions, long-term strategies, national adaptation plans and adaptation communications, as reported to the secretariat of the United Nations Framework Convention on Climate Change</t>
+    <t>13.3.1</t>
+  </si>
+  <si>
+    <t>13.3</t>
   </si>
   <si>
     <t>13.a.1</t>
@@ -1303,6 +1402,42 @@
     <t>14.1</t>
   </si>
   <si>
+    <t>14.2.1</t>
+  </si>
+  <si>
+    <t>Number of countries using ecosystem-based approaches to managing marine areas</t>
+  </si>
+  <si>
+    <t>14.2</t>
+  </si>
+  <si>
+    <t>14.3.1</t>
+  </si>
+  <si>
+    <t>Average marine acidity (pH) measured at agreed suite of representative sampling stations</t>
+  </si>
+  <si>
+    <t>14.3</t>
+  </si>
+  <si>
+    <t>14.4.1</t>
+  </si>
+  <si>
+    <t>Proportion of fish stocks within biologically sustainable levels</t>
+  </si>
+  <si>
+    <t>14.4</t>
+  </si>
+  <si>
+    <t>14.5.1</t>
+  </si>
+  <si>
+    <t>Coverage of protected areas in relation to marine areas</t>
+  </si>
+  <si>
+    <t>14.5</t>
+  </si>
+  <si>
     <t>14.6.1</t>
   </si>
   <si>
@@ -1321,15 +1456,6 @@
     <t>14.7</t>
   </si>
   <si>
-    <t>14.3.1</t>
-  </si>
-  <si>
-    <t>Average marine acidity (pH) measured at agreed suite of representative sampling stations</t>
-  </si>
-  <si>
-    <t>14.3</t>
-  </si>
-  <si>
     <t>14.a.1</t>
   </si>
   <si>
@@ -1339,33 +1465,15 @@
     <t>14.a</t>
   </si>
   <si>
-    <t>14.4.1</t>
-  </si>
-  <si>
-    <t>Proportion of fish stocks within biologically sustainable levels</t>
-  </si>
-  <si>
-    <t>14.4</t>
-  </si>
-  <si>
     <t>14.b.1</t>
   </si>
   <si>
-    <t>Degree of application of a legal/regulatory/policy/institutional framework which recognizes and protects access rights for small-scale fisheries</t>
+    <t>Degree of application of a legal/regulatory/ policy/institutional framework which recognizes and protects access rights for small-scale fisheries</t>
   </si>
   <si>
     <t>14.b</t>
   </si>
   <si>
-    <t>14.5.1</t>
-  </si>
-  <si>
-    <t>Coverage of protected areas in relation to marine areas</t>
-  </si>
-  <si>
-    <t>14.5</t>
-  </si>
-  <si>
     <t>14.c.1</t>
   </si>
   <si>
@@ -1441,6 +1549,15 @@
     <t>15.6</t>
   </si>
   <si>
+    <t>15.7.1</t>
+  </si>
+  <si>
+    <t>Proportion of traded wildlife that was poached or illicitly trafficked</t>
+  </si>
+  <si>
+    <t>15.7</t>
+  </si>
+  <si>
     <t>15.8.1</t>
   </si>
   <si>
@@ -1474,6 +1591,12 @@
     <t>15.b</t>
   </si>
   <si>
+    <t>15.c.1</t>
+  </si>
+  <si>
+    <t>15.c</t>
+  </si>
+  <si>
     <t>16.1.1</t>
   </si>
   <si>
@@ -1483,6 +1606,12 @@
     <t>16.1</t>
   </si>
   <si>
+    <t>16.1.2</t>
+  </si>
+  <si>
+    <t>Conflict-related deaths per 100,000 population, by sex, age and cause</t>
+  </si>
+  <si>
     <t>16.1.3</t>
   </si>
   <si>
@@ -1495,12 +1624,6 @@
     <t>Proportion of population that feel safe walking alone around the area they live</t>
   </si>
   <si>
-    <t>16.1.2</t>
-  </si>
-  <si>
-    <t>Conflict-related deaths per 100,000 population, by sex, age and cause</t>
-  </si>
-  <si>
     <t>16.2.1</t>
   </si>
   <si>
@@ -1522,19 +1645,34 @@
     <t>Proportion of young women and men aged 18-29 years who experienced sexual violence by age 18</t>
   </si>
   <si>
+    <t>16.3.1</t>
+  </si>
+  <si>
+    <t>Proportion of victims of violence in the previous 12 months who reported their victimization to competent authorities or other officially recognized conflict resolution mechanisms</t>
+  </si>
+  <si>
+    <t>16.3</t>
+  </si>
+  <si>
     <t>16.3.2</t>
   </si>
   <si>
     <t>Unsentenced detainees as a proportion of overall prison population</t>
   </si>
   <si>
-    <t>16.3</t>
-  </si>
-  <si>
-    <t>16.3.1</t>
-  </si>
-  <si>
-    <t>Proportion of victims of violence in the previous 12 months who reported their victimization to competent authorities or other officially recognized conflict resolution mechanisms</t>
+    <t>16.3.3</t>
+  </si>
+  <si>
+    <t>Proportion of the population who have experienced a dispute in the past two years and who accessed a formal or informal dispute resolution mechanism, by type of mechanism</t>
+  </si>
+  <si>
+    <t>16.4.1</t>
+  </si>
+  <si>
+    <t>Total value of inward and outward illicit financial flows (in current United States dollars)</t>
+  </si>
+  <si>
+    <t>16.4</t>
   </si>
   <si>
     <t>16.4.2</t>
@@ -1543,7 +1681,13 @@
     <t>Proportion of seized, found or surrendered arms whose illicit origin or context has been traced or established by a competent authority in line with international instruments</t>
   </si>
   <si>
-    <t>16.4</t>
+    <t>16.5.1</t>
+  </si>
+  <si>
+    <t>Proportion of persons who had at least one contact with a public official and who paid a bribe to a public official, or were asked for a bribe by those public officials, during the previous 12 months</t>
+  </si>
+  <si>
+    <t>16.5</t>
   </si>
   <si>
     <t>16.5.2</t>
@@ -1552,15 +1696,6 @@
     <t>Proportion of businesses that had at least one contact with a public official and that paid a bribe to a public official, or were asked for a bribe by those public officials during the previous 12 months</t>
   </si>
   <si>
-    <t>16.5</t>
-  </si>
-  <si>
-    <t>16.5.1</t>
-  </si>
-  <si>
-    <t>Proportion of persons who had at least one contact with a public official and who paid a bribe to a public official, or were asked for a bribe by those public officials, during the previous 12 months</t>
-  </si>
-  <si>
     <t>16.6.1</t>
   </si>
   <si>
@@ -1570,6 +1705,12 @@
     <t>16.6</t>
   </si>
   <si>
+    <t>16.6.2</t>
+  </si>
+  <si>
+    <t>Proportion of population satisfied with their last experience of public services</t>
+  </si>
+  <si>
     <t>16.7.1</t>
   </si>
   <si>
@@ -1579,6 +1720,12 @@
     <t>16.7</t>
   </si>
   <si>
+    <t>16.7.2</t>
+  </si>
+  <si>
+    <t>Proportion of population who believe decision-making is inclusive and responsive, by sex, age, disability and population group</t>
+  </si>
+  <si>
     <t>16.8.1</t>
   </si>
   <si>
@@ -1648,21 +1795,21 @@
     <t>17.2</t>
   </si>
   <si>
+    <t>17.3.1</t>
+  </si>
+  <si>
+    <t>Foreign direct investment, official development assistance and South-South cooperation as a proportion of gross national income</t>
+  </si>
+  <si>
+    <t>17.3</t>
+  </si>
+  <si>
     <t>17.3.2</t>
   </si>
   <si>
     <t>Volume of remittances (in United States dollars) as a proportion of total GDP</t>
   </si>
   <si>
-    <t>17.3</t>
-  </si>
-  <si>
-    <t>17.3.1</t>
-  </si>
-  <si>
-    <t>Foreign direct investment, official development assistance and South-South cooperation as a proportion of gross national income</t>
-  </si>
-  <si>
     <t>17.4.1</t>
   </si>
   <si>
@@ -1690,6 +1837,15 @@
     <t>17.6</t>
   </si>
   <si>
+    <t>17.7.1</t>
+  </si>
+  <si>
+    <t>Total amount of funding for developing countries to promote the development, transfer, dissemination and diffusion of environmentally sound technologies</t>
+  </si>
+  <si>
+    <t>17.7</t>
+  </si>
+  <si>
     <t>17.8.1</t>
   </si>
   <si>
@@ -1735,6 +1891,15 @@
     <t>17.12</t>
   </si>
   <si>
+    <t>17.13.1</t>
+  </si>
+  <si>
+    <t>Macroeconomic Dashboard</t>
+  </si>
+  <si>
+    <t>17.13</t>
+  </si>
+  <si>
     <t>17.14.1</t>
   </si>
   <si>
@@ -1771,13 +1936,19 @@
     <t>17.17</t>
   </si>
   <si>
+    <t>17.18.1</t>
+  </si>
+  <si>
+    <t>Statistical capacity indicator for Sustainable Development Goal monitoring</t>
+  </si>
+  <si>
+    <t>17.18</t>
+  </si>
+  <si>
     <t>17.18.2</t>
   </si>
   <si>
     <t>Number of countries that have national statistical legislation that complies with the Fundamental Principles of Official Statistics</t>
-  </si>
-  <si>
-    <t>17.18</t>
   </si>
   <si>
     <t>17.18.3</t>
@@ -2130,7 +2301,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D225"/>
+  <dimension ref="A1:D248"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2337,7 +2508,7 @@
         <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -2345,13 +2516,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" t="s">
         <v>40</v>
-      </c>
-      <c r="B16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" t="s">
-        <v>42</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -2365,7 +2536,7 @@
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -2373,13 +2544,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
         <v>45</v>
-      </c>
-      <c r="B18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" t="s">
-        <v>42</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -2387,13 +2558,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -2407,7 +2578,7 @@
         <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -2415,13 +2586,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" t="s">
         <v>52</v>
-      </c>
-      <c r="B21" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" t="s">
-        <v>54</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -2435,7 +2606,7 @@
         <v>56</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -2443,13 +2614,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -2457,13 +2628,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" t="s">
         <v>60</v>
-      </c>
-      <c r="B24" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" t="s">
-        <v>59</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -2471,13 +2642,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -2485,13 +2656,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
         <v>65</v>
-      </c>
-      <c r="B26" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" t="s">
-        <v>67</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -2519,7 +2690,7 @@
         <v>72</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -2527,13 +2698,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -2541,13 +2712,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" t="s">
         <v>76</v>
-      </c>
-      <c r="B30" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" t="s">
-        <v>75</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -2555,13 +2726,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -2569,13 +2740,13 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" t="s">
         <v>81</v>
-      </c>
-      <c r="B32" t="s">
-        <v>82</v>
-      </c>
-      <c r="C32" t="s">
-        <v>80</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -2583,13 +2754,13 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -2597,13 +2768,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B34" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" t="s">
         <v>86</v>
-      </c>
-      <c r="C34" t="s">
-        <v>80</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -2611,13 +2782,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -2625,13 +2796,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B36" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C36" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -2639,13 +2810,13 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C37" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -2653,13 +2824,13 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B38" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -2667,13 +2838,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
+        <v>98</v>
+      </c>
+      <c r="B39" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" t="s">
         <v>97</v>
-      </c>
-      <c r="B39" t="s">
-        <v>98</v>
-      </c>
-      <c r="C39" t="s">
-        <v>96</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -2681,13 +2852,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -2695,13 +2866,13 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41" t="s">
+        <v>104</v>
+      </c>
+      <c r="C41" t="s">
         <v>102</v>
-      </c>
-      <c r="B41" t="s">
-        <v>103</v>
-      </c>
-      <c r="C41" t="s">
-        <v>104</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -2715,7 +2886,7 @@
         <v>106</v>
       </c>
       <c r="C42" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -2723,13 +2894,13 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C43" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -2737,13 +2908,13 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" t="s">
+        <v>112</v>
+      </c>
+      <c r="C44" t="s">
         <v>110</v>
-      </c>
-      <c r="B44" t="s">
-        <v>111</v>
-      </c>
-      <c r="C44" t="s">
-        <v>109</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -2751,13 +2922,13 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B45" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -2765,13 +2936,13 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
+        <v>116</v>
+      </c>
+      <c r="B46" t="s">
+        <v>117</v>
+      </c>
+      <c r="C46" t="s">
         <v>115</v>
-      </c>
-      <c r="B46" t="s">
-        <v>116</v>
-      </c>
-      <c r="C46" t="s">
-        <v>114</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -2779,13 +2950,13 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C47" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -2793,13 +2964,13 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B48" t="s">
+        <v>122</v>
+      </c>
+      <c r="C48" t="s">
         <v>120</v>
-      </c>
-      <c r="C48" t="s">
-        <v>121</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -2807,13 +2978,13 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B49" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C49" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -2827,7 +2998,7 @@
         <v>126</v>
       </c>
       <c r="C50" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -2835,13 +3006,13 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B51" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C51" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -2849,13 +3020,13 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B52" t="s">
+        <v>132</v>
+      </c>
+      <c r="C52" t="s">
         <v>130</v>
-      </c>
-      <c r="C52" t="s">
-        <v>131</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -2863,13 +3034,13 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B53" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C53" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -2883,7 +3054,7 @@
         <v>136</v>
       </c>
       <c r="C54" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -2891,13 +3062,13 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B55" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C55" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -2905,13 +3076,13 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
+        <v>141</v>
+      </c>
+      <c r="B56" t="s">
+        <v>142</v>
+      </c>
+      <c r="C56" t="s">
         <v>140</v>
-      </c>
-      <c r="B56" t="s">
-        <v>141</v>
-      </c>
-      <c r="C56" t="s">
-        <v>139</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -2919,13 +3090,13 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B57" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C57" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -2933,13 +3104,13 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
+        <v>146</v>
+      </c>
+      <c r="B58" t="s">
+        <v>147</v>
+      </c>
+      <c r="C58" t="s">
         <v>145</v>
-      </c>
-      <c r="B58" t="s">
-        <v>146</v>
-      </c>
-      <c r="C58" t="s">
-        <v>144</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -2947,13 +3118,13 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B59" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C59" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -2961,13 +3132,13 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
+        <v>151</v>
+      </c>
+      <c r="B60" t="s">
+        <v>152</v>
+      </c>
+      <c r="C60" t="s">
         <v>150</v>
-      </c>
-      <c r="B60" t="s">
-        <v>151</v>
-      </c>
-      <c r="C60" t="s">
-        <v>152</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -3093,7 +3264,7 @@
         <v>178</v>
       </c>
       <c r="C69" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
@@ -3101,13 +3272,13 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B70" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C70" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
@@ -3115,13 +3286,13 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
+        <v>183</v>
+      </c>
+      <c r="B71" t="s">
+        <v>184</v>
+      </c>
+      <c r="C71" t="s">
         <v>182</v>
-      </c>
-      <c r="B71" t="s">
-        <v>183</v>
-      </c>
-      <c r="C71" t="s">
-        <v>184</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
@@ -3135,7 +3306,7 @@
         <v>186</v>
       </c>
       <c r="C72" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
@@ -3143,13 +3314,13 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
+        <v>188</v>
+      </c>
+      <c r="B73" t="s">
+        <v>189</v>
+      </c>
+      <c r="C73" t="s">
         <v>187</v>
-      </c>
-      <c r="B73" t="s">
-        <v>188</v>
-      </c>
-      <c r="C73" t="s">
-        <v>189</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
@@ -3163,7 +3334,7 @@
         <v>191</v>
       </c>
       <c r="C74" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
@@ -3171,13 +3342,13 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B75" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C75" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
@@ -3185,13 +3356,13 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
+        <v>196</v>
+      </c>
+      <c r="B76" t="s">
+        <v>197</v>
+      </c>
+      <c r="C76" t="s">
         <v>195</v>
-      </c>
-      <c r="B76" t="s">
-        <v>196</v>
-      </c>
-      <c r="C76" t="s">
-        <v>194</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
@@ -3199,13 +3370,13 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B77" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C77" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -3213,13 +3384,13 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
+        <v>201</v>
+      </c>
+      <c r="B78" t="s">
+        <v>202</v>
+      </c>
+      <c r="C78" t="s">
         <v>200</v>
-      </c>
-      <c r="B78" t="s">
-        <v>201</v>
-      </c>
-      <c r="C78" t="s">
-        <v>202</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
@@ -3247,7 +3418,7 @@
         <v>207</v>
       </c>
       <c r="C80" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
@@ -3255,13 +3426,13 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
+        <v>208</v>
+      </c>
+      <c r="B81" t="s">
         <v>209</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>210</v>
-      </c>
-      <c r="C81" t="s">
-        <v>211</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
@@ -3269,13 +3440,13 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
+        <v>211</v>
+      </c>
+      <c r="B82" t="s">
         <v>212</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>213</v>
-      </c>
-      <c r="C82" t="s">
-        <v>211</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -3303,7 +3474,7 @@
         <v>218</v>
       </c>
       <c r="C84" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -3311,13 +3482,13 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B85" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C85" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
@@ -3325,13 +3496,13 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
+        <v>223</v>
+      </c>
+      <c r="B86" t="s">
+        <v>224</v>
+      </c>
+      <c r="C86" t="s">
         <v>222</v>
-      </c>
-      <c r="B86" t="s">
-        <v>223</v>
-      </c>
-      <c r="C86" t="s">
-        <v>221</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
@@ -3339,13 +3510,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B87" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C87" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
@@ -3353,13 +3524,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
+        <v>228</v>
+      </c>
+      <c r="B88" t="s">
+        <v>229</v>
+      </c>
+      <c r="C88" t="s">
         <v>227</v>
-      </c>
-      <c r="B88" t="s">
-        <v>228</v>
-      </c>
-      <c r="C88" t="s">
-        <v>229</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
@@ -3387,7 +3558,7 @@
         <v>234</v>
       </c>
       <c r="C90" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -3395,13 +3566,13 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
+        <v>235</v>
+      </c>
+      <c r="B91" t="s">
         <v>236</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>237</v>
-      </c>
-      <c r="C91" t="s">
-        <v>235</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
@@ -3457,7 +3628,7 @@
         <v>248</v>
       </c>
       <c r="C95" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
@@ -3465,13 +3636,13 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
+        <v>249</v>
+      </c>
+      <c r="B96" t="s">
         <v>250</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" t="s">
         <v>251</v>
-      </c>
-      <c r="C96" t="s">
-        <v>252</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
@@ -3479,13 +3650,13 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
+        <v>252</v>
+      </c>
+      <c r="B97" t="s">
         <v>253</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>254</v>
-      </c>
-      <c r="C97" t="s">
-        <v>255</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
@@ -3493,13 +3664,13 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
+        <v>255</v>
+      </c>
+      <c r="B98" t="s">
         <v>256</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C98" t="s">
         <v>257</v>
-      </c>
-      <c r="C98" t="s">
-        <v>258</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
@@ -3507,13 +3678,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
+        <v>258</v>
+      </c>
+      <c r="B99" t="s">
         <v>259</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
         <v>260</v>
-      </c>
-      <c r="C99" t="s">
-        <v>258</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -3541,7 +3712,7 @@
         <v>265</v>
       </c>
       <c r="C101" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
@@ -3549,13 +3720,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B102" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C102" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
@@ -3563,13 +3734,13 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B103" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C103" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -3577,13 +3748,13 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
+        <v>273</v>
+      </c>
+      <c r="B104" t="s">
+        <v>274</v>
+      </c>
+      <c r="C104" t="s">
         <v>272</v>
-      </c>
-      <c r="B104" t="s">
-        <v>273</v>
-      </c>
-      <c r="C104" t="s">
-        <v>274</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
@@ -3653,7 +3824,7 @@
         <v>287</v>
       </c>
       <c r="C109" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D109" t="s">
         <v>7</v>
@@ -3661,13 +3832,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
+        <v>289</v>
+      </c>
+      <c r="B110" t="s">
+        <v>290</v>
+      </c>
+      <c r="C110" t="s">
         <v>288</v>
-      </c>
-      <c r="B110" t="s">
-        <v>289</v>
-      </c>
-      <c r="C110" t="s">
-        <v>290</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -3737,7 +3908,7 @@
         <v>303</v>
       </c>
       <c r="C115" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -3745,13 +3916,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B116" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C116" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -3759,13 +3930,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
+        <v>308</v>
+      </c>
+      <c r="B117" t="s">
+        <v>309</v>
+      </c>
+      <c r="C117" t="s">
         <v>307</v>
-      </c>
-      <c r="B117" t="s">
-        <v>308</v>
-      </c>
-      <c r="C117" t="s">
-        <v>306</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -3773,13 +3944,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B118" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C118" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -3787,13 +3958,13 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
+        <v>313</v>
+      </c>
+      <c r="B119" t="s">
+        <v>314</v>
+      </c>
+      <c r="C119" t="s">
         <v>312</v>
-      </c>
-      <c r="B119" t="s">
-        <v>313</v>
-      </c>
-      <c r="C119" t="s">
-        <v>314</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -3807,7 +3978,7 @@
         <v>316</v>
       </c>
       <c r="C120" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -3815,13 +3986,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
+        <v>318</v>
+      </c>
+      <c r="B121" t="s">
+        <v>319</v>
+      </c>
+      <c r="C121" t="s">
         <v>317</v>
-      </c>
-      <c r="B121" t="s">
-        <v>318</v>
-      </c>
-      <c r="C121" t="s">
-        <v>319</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -3863,7 +4034,7 @@
         <v>327</v>
       </c>
       <c r="C124" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -3871,13 +4042,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
+        <v>328</v>
+      </c>
+      <c r="B125" t="s">
         <v>329</v>
       </c>
-      <c r="B125" t="s">
+      <c r="C125" t="s">
         <v>330</v>
-      </c>
-      <c r="C125" t="s">
-        <v>331</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -3885,13 +4056,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
+        <v>331</v>
+      </c>
+      <c r="B126" t="s">
         <v>332</v>
       </c>
-      <c r="B126" t="s">
+      <c r="C126" t="s">
         <v>333</v>
-      </c>
-      <c r="C126" t="s">
-        <v>334</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -3899,13 +4070,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
+        <v>334</v>
+      </c>
+      <c r="B127" t="s">
         <v>335</v>
       </c>
-      <c r="B127" t="s">
+      <c r="C127" t="s">
         <v>336</v>
-      </c>
-      <c r="C127" t="s">
-        <v>337</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -3913,13 +4084,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
+        <v>337</v>
+      </c>
+      <c r="B128" t="s">
         <v>338</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" t="s">
         <v>339</v>
-      </c>
-      <c r="C128" t="s">
-        <v>337</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -3989,7 +4160,7 @@
         <v>352</v>
       </c>
       <c r="C133" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -3997,13 +4168,13 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B134" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C134" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -4011,13 +4182,13 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B135" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C135" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -4025,13 +4196,13 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" t="s">
+        <v>360</v>
+      </c>
+      <c r="B136" t="s">
+        <v>361</v>
+      </c>
+      <c r="C136" t="s">
         <v>359</v>
-      </c>
-      <c r="B136" t="s">
-        <v>360</v>
-      </c>
-      <c r="C136" t="s">
-        <v>361</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -4045,7 +4216,7 @@
         <v>363</v>
       </c>
       <c r="C137" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -4053,13 +4224,13 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
+        <v>364</v>
+      </c>
+      <c r="B138" t="s">
         <v>365</v>
       </c>
-      <c r="B138" t="s">
-        <v>22</v>
-      </c>
       <c r="C138" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -4067,13 +4238,13 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
+        <v>366</v>
+      </c>
+      <c r="B139" t="s">
         <v>367</v>
       </c>
-      <c r="B139" t="s">
+      <c r="C139" t="s">
         <v>368</v>
-      </c>
-      <c r="C139" t="s">
-        <v>366</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -4101,7 +4272,7 @@
         <v>373</v>
       </c>
       <c r="C141" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -4109,13 +4280,13 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B142" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C142" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -4123,13 +4294,13 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B143" t="s">
-        <v>27</v>
+        <v>379</v>
       </c>
       <c r="C143" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -4137,13 +4308,13 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B144" t="s">
-        <v>29</v>
+        <v>382</v>
       </c>
       <c r="C144" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -4151,13 +4322,13 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B145" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C145" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -4165,13 +4336,13 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B146" t="s">
-        <v>257</v>
+        <v>387</v>
       </c>
       <c r="C146" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -4179,13 +4350,13 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B147" t="s">
-        <v>260</v>
+        <v>22</v>
       </c>
       <c r="C147" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -4193,13 +4364,13 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B148" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C148" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -4207,13 +4378,13 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B149" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C149" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -4221,13 +4392,13 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B150" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C150" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -4235,13 +4406,13 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B151" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C151" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -4249,13 +4420,13 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B152" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C152" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -4263,13 +4434,13 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B153" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C153" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -4277,13 +4448,13 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B154" t="s">
-        <v>248</v>
+        <v>27</v>
       </c>
       <c r="C154" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -4291,10 +4462,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B155" t="s">
-        <v>406</v>
+        <v>29</v>
       </c>
       <c r="C155" t="s">
         <v>407</v>
@@ -4305,13 +4476,13 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B156" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C156" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -4319,13 +4490,13 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B157" t="s">
-        <v>22</v>
+        <v>271</v>
       </c>
       <c r="C157" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -4333,13 +4504,13 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" t="s">
+        <v>414</v>
+      </c>
+      <c r="B158" t="s">
+        <v>274</v>
+      </c>
+      <c r="C158" t="s">
         <v>413</v>
-      </c>
-      <c r="B158" t="s">
-        <v>27</v>
-      </c>
-      <c r="C158" t="s">
-        <v>412</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -4347,13 +4518,13 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B159" t="s">
-        <v>29</v>
+        <v>416</v>
       </c>
       <c r="C159" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -4361,13 +4532,13 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B160" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C160" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -4375,13 +4546,13 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B161" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C161" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -4389,13 +4560,13 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B162" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C162" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -4403,13 +4574,13 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B163" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C163" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -4417,13 +4588,13 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C164" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -4431,13 +4602,13 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B165" t="s">
-        <v>430</v>
+        <v>166</v>
       </c>
       <c r="C165" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -4445,13 +4616,13 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B166" t="s">
-        <v>433</v>
+        <v>259</v>
       </c>
       <c r="C166" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -4459,13 +4630,13 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B167" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C167" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -4473,13 +4644,13 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B168" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C168" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -4487,10 +4658,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B169" t="s">
-        <v>442</v>
+        <v>22</v>
       </c>
       <c r="C169" t="s">
         <v>443</v>
@@ -4504,10 +4675,10 @@
         <v>444</v>
       </c>
       <c r="B170" t="s">
-        <v>445</v>
+        <v>27</v>
       </c>
       <c r="C170" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -4515,13 +4686,13 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B171" t="s">
-        <v>448</v>
+        <v>29</v>
       </c>
       <c r="C171" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -4529,13 +4700,13 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B172" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C172" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -4543,13 +4714,13 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B173" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C173" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -4557,13 +4728,13 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B174" t="s">
-        <v>457</v>
+        <v>166</v>
       </c>
       <c r="C174" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -4571,13 +4742,13 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B175" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C175" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -4585,13 +4756,13 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="B176" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="C176" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -4599,13 +4770,13 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B177" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C177" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -4613,13 +4784,13 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="B178" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C178" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -4627,13 +4798,13 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B179" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C179" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -4641,13 +4812,13 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="B180" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C180" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -4655,13 +4826,13 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B181" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C181" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -4669,13 +4840,13 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B182" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C182" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -4683,13 +4854,13 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B183" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C183" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -4697,13 +4868,13 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B184" t="s">
+        <v>481</v>
+      </c>
+      <c r="C184" t="s">
         <v>482</v>
-      </c>
-      <c r="C184" t="s">
-        <v>485</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -4711,13 +4882,13 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B185" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C185" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -4725,10 +4896,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B186" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C186" t="s">
         <v>488</v>
@@ -4739,13 +4910,13 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
+        <v>489</v>
+      </c>
+      <c r="B187" t="s">
+        <v>490</v>
+      </c>
+      <c r="C187" t="s">
         <v>491</v>
-      </c>
-      <c r="B187" t="s">
-        <v>492</v>
-      </c>
-      <c r="C187" t="s">
-        <v>488</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -4753,13 +4924,13 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
+        <v>492</v>
+      </c>
+      <c r="B188" t="s">
         <v>493</v>
       </c>
-      <c r="B188" t="s">
-        <v>494</v>
-      </c>
       <c r="C188" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -4767,13 +4938,13 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
+        <v>494</v>
+      </c>
+      <c r="B189" t="s">
         <v>495</v>
       </c>
-      <c r="B189" t="s">
+      <c r="C189" t="s">
         <v>496</v>
-      </c>
-      <c r="C189" t="s">
-        <v>497</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -4781,13 +4952,13 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
+        <v>497</v>
+      </c>
+      <c r="B190" t="s">
         <v>498</v>
       </c>
-      <c r="B190" t="s">
+      <c r="C190" t="s">
         <v>499</v>
-      </c>
-      <c r="C190" t="s">
-        <v>497</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -4801,7 +4972,7 @@
         <v>501</v>
       </c>
       <c r="C191" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -4809,13 +4980,13 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
+        <v>503</v>
+      </c>
+      <c r="B192" t="s">
+        <v>504</v>
+      </c>
+      <c r="C192" t="s">
         <v>502</v>
-      </c>
-      <c r="B192" t="s">
-        <v>503</v>
-      </c>
-      <c r="C192" t="s">
-        <v>504</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -4829,7 +5000,7 @@
         <v>506</v>
       </c>
       <c r="C193" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -4837,13 +5008,13 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B194" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C194" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -4851,13 +5022,13 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B195" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C195" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -4865,13 +5036,13 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B196" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C196" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -4879,13 +5050,13 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B197" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C197" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -4893,13 +5064,13 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B198" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C198" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -4907,13 +5078,13 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" t="s">
+        <v>523</v>
+      </c>
+      <c r="B199" t="s">
         <v>521</v>
       </c>
-      <c r="B199" t="s">
-        <v>344</v>
-      </c>
       <c r="C199" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -4921,13 +5092,13 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B200" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="C200" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -4935,13 +5106,13 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B201" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C201" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -4949,13 +5120,13 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
+        <v>530</v>
+      </c>
+      <c r="B202" t="s">
+        <v>531</v>
+      </c>
+      <c r="C202" t="s">
         <v>529</v>
-      </c>
-      <c r="B202" t="s">
-        <v>530</v>
-      </c>
-      <c r="C202" t="s">
-        <v>528</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -4963,13 +5134,13 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B203" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C203" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -4980,10 +5151,10 @@
         <v>534</v>
       </c>
       <c r="B204" t="s">
-        <v>333</v>
+        <v>535</v>
       </c>
       <c r="C204" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -5025,7 +5196,7 @@
         <v>542</v>
       </c>
       <c r="C207" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -5033,13 +5204,13 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
+        <v>543</v>
+      </c>
+      <c r="B208" t="s">
         <v>544</v>
       </c>
-      <c r="B208" t="s">
+      <c r="C208" t="s">
         <v>545</v>
-      </c>
-      <c r="C208" t="s">
-        <v>546</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -5047,13 +5218,13 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
+        <v>546</v>
+      </c>
+      <c r="B209" t="s">
         <v>547</v>
       </c>
-      <c r="B209" t="s">
-        <v>548</v>
-      </c>
       <c r="C209" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -5061,13 +5232,13 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
+        <v>548</v>
+      </c>
+      <c r="B210" t="s">
         <v>549</v>
       </c>
-      <c r="B210" t="s">
-        <v>550</v>
-      </c>
       <c r="C210" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -5075,13 +5246,13 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
+        <v>550</v>
+      </c>
+      <c r="B211" t="s">
+        <v>551</v>
+      </c>
+      <c r="C211" t="s">
         <v>552</v>
-      </c>
-      <c r="B211" t="s">
-        <v>553</v>
-      </c>
-      <c r="C211" t="s">
-        <v>554</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -5089,13 +5260,13 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B212" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C212" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -5103,13 +5274,13 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B213" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C213" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -5117,13 +5288,13 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B214" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C214" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -5131,13 +5302,13 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="B215" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="C215" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -5145,13 +5316,13 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B216" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C216" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -5159,13 +5330,13 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="B217" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C217" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -5173,13 +5344,13 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="B218" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="C218" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -5187,13 +5358,13 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="B219" t="s">
-        <v>577</v>
+        <v>355</v>
       </c>
       <c r="C219" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -5201,13 +5372,13 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="B220" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="C220" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -5215,13 +5386,13 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="B221" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="C221" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -5229,13 +5400,13 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="B222" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="C222" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -5243,13 +5414,13 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="B223" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="C223" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -5257,13 +5428,13 @@
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="B224" t="s">
-        <v>591</v>
+        <v>344</v>
       </c>
       <c r="C224" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -5271,15 +5442,337 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
+        <v>585</v>
+      </c>
+      <c r="B225" t="s">
+        <v>586</v>
+      </c>
+      <c r="C225" t="s">
+        <v>587</v>
+      </c>
+      <c r="D225" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" t="s">
+        <v>588</v>
+      </c>
+      <c r="B226" t="s">
+        <v>589</v>
+      </c>
+      <c r="C226" t="s">
+        <v>587</v>
+      </c>
+      <c r="D226" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" t="s">
+        <v>590</v>
+      </c>
+      <c r="B227" t="s">
+        <v>591</v>
+      </c>
+      <c r="C227" t="s">
+        <v>592</v>
+      </c>
+      <c r="D227" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" t="s">
         <v>593</v>
       </c>
-      <c r="B225" t="s">
+      <c r="B228" t="s">
         <v>594</v>
       </c>
-      <c r="C225" t="s">
-        <v>592</v>
-      </c>
-      <c r="D225" t="s">
+      <c r="C228" t="s">
+        <v>595</v>
+      </c>
+      <c r="D228" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" t="s">
+        <v>596</v>
+      </c>
+      <c r="B229" t="s">
+        <v>597</v>
+      </c>
+      <c r="C229" t="s">
+        <v>595</v>
+      </c>
+      <c r="D229" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
+      <c r="A230" t="s">
+        <v>598</v>
+      </c>
+      <c r="B230" t="s">
+        <v>599</v>
+      </c>
+      <c r="C230" t="s">
+        <v>600</v>
+      </c>
+      <c r="D230" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="A231" t="s">
+        <v>601</v>
+      </c>
+      <c r="B231" t="s">
+        <v>602</v>
+      </c>
+      <c r="C231" t="s">
+        <v>603</v>
+      </c>
+      <c r="D231" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
+      <c r="A232" t="s">
+        <v>604</v>
+      </c>
+      <c r="B232" t="s">
+        <v>605</v>
+      </c>
+      <c r="C232" t="s">
+        <v>606</v>
+      </c>
+      <c r="D232" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
+      <c r="A233" t="s">
+        <v>607</v>
+      </c>
+      <c r="B233" t="s">
+        <v>608</v>
+      </c>
+      <c r="C233" t="s">
+        <v>609</v>
+      </c>
+      <c r="D233" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
+      <c r="A234" t="s">
+        <v>610</v>
+      </c>
+      <c r="B234" t="s">
+        <v>611</v>
+      </c>
+      <c r="C234" t="s">
+        <v>612</v>
+      </c>
+      <c r="D234" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
+      <c r="A235" t="s">
+        <v>613</v>
+      </c>
+      <c r="B235" t="s">
+        <v>614</v>
+      </c>
+      <c r="C235" t="s">
+        <v>615</v>
+      </c>
+      <c r="D235" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" t="s">
+        <v>616</v>
+      </c>
+      <c r="B236" t="s">
+        <v>617</v>
+      </c>
+      <c r="C236" t="s">
+        <v>618</v>
+      </c>
+      <c r="D236" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" t="s">
+        <v>619</v>
+      </c>
+      <c r="B237" t="s">
+        <v>620</v>
+      </c>
+      <c r="C237" t="s">
+        <v>621</v>
+      </c>
+      <c r="D237" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
+      <c r="A238" t="s">
+        <v>622</v>
+      </c>
+      <c r="B238" t="s">
+        <v>623</v>
+      </c>
+      <c r="C238" t="s">
+        <v>624</v>
+      </c>
+      <c r="D238" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" t="s">
+        <v>625</v>
+      </c>
+      <c r="B239" t="s">
+        <v>626</v>
+      </c>
+      <c r="C239" t="s">
+        <v>627</v>
+      </c>
+      <c r="D239" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" t="s">
+        <v>628</v>
+      </c>
+      <c r="B240" t="s">
+        <v>629</v>
+      </c>
+      <c r="C240" t="s">
+        <v>630</v>
+      </c>
+      <c r="D240" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" t="s">
+        <v>631</v>
+      </c>
+      <c r="B241" t="s">
+        <v>632</v>
+      </c>
+      <c r="C241" t="s">
+        <v>633</v>
+      </c>
+      <c r="D241" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" t="s">
+        <v>634</v>
+      </c>
+      <c r="B242" t="s">
+        <v>635</v>
+      </c>
+      <c r="C242" t="s">
+        <v>636</v>
+      </c>
+      <c r="D242" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
+      <c r="A243" t="s">
+        <v>637</v>
+      </c>
+      <c r="B243" t="s">
+        <v>638</v>
+      </c>
+      <c r="C243" t="s">
+        <v>639</v>
+      </c>
+      <c r="D243" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4">
+      <c r="A244" t="s">
+        <v>640</v>
+      </c>
+      <c r="B244" t="s">
+        <v>641</v>
+      </c>
+      <c r="C244" t="s">
+        <v>642</v>
+      </c>
+      <c r="D244" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
+      <c r="A245" t="s">
+        <v>643</v>
+      </c>
+      <c r="B245" t="s">
+        <v>644</v>
+      </c>
+      <c r="C245" t="s">
+        <v>642</v>
+      </c>
+      <c r="D245" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
+      <c r="A246" t="s">
+        <v>645</v>
+      </c>
+      <c r="B246" t="s">
+        <v>646</v>
+      </c>
+      <c r="C246" t="s">
+        <v>642</v>
+      </c>
+      <c r="D246" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4">
+      <c r="A247" t="s">
+        <v>647</v>
+      </c>
+      <c r="B247" t="s">
+        <v>648</v>
+      </c>
+      <c r="C247" t="s">
+        <v>649</v>
+      </c>
+      <c r="D247" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
+      <c r="A248" t="s">
+        <v>650</v>
+      </c>
+      <c r="B248" t="s">
+        <v>651</v>
+      </c>
+      <c r="C248" t="s">
+        <v>649</v>
+      </c>
+      <c r="D248" t="s">
         <v>7</v>
       </c>
     </row>

--- a/api/clv2/xlsx/en/UNSDG-Indicators.xlsx
+++ b/api/clv2/xlsx/en/UNSDG-Indicators.xlsx
@@ -97,7 +97,7 @@
     <t>1.5.3</t>
   </si>
   <si>
-    <t>Number of countries that adopt and implement national disaster risk reduction strategies in line with the Sendai Framework for Disaster Risk Reduction 2015-2030</t>
+    <t>Number of countries that adopt and implement national disaster risk reduction strategies in line with the Sendai Framework for Disaster Risk Reduction 2015–2030</t>
   </si>
   <si>
     <t>1.5.4</t>
@@ -343,7 +343,7 @@
     <t>3.7.1</t>
   </si>
   <si>
-    <t>Proportion of women of reproductive age (aged 15-49 years) who have their need for family planning satisfied with modern methods</t>
+    <t>Proportion of women of reproductive age (aged 15–49 years) who have their need for family planning satisfied with modern methods</t>
   </si>
   <si>
     <t>3.7</t>
@@ -352,7 +352,7 @@
     <t>3.7.2</t>
   </si>
   <si>
-    <t>Adolescent birth rate (aged 10-14 years; aged 15-19 years) per 1,000 women in that age group</t>
+    <t>Adolescent birth rate (aged 10–14 years; aged 15–19 years) per 1,000 women in that age group</t>
   </si>
   <si>
     <t>3.8.1</t>
@@ -463,7 +463,7 @@
     <t>4.2.1</t>
   </si>
   <si>
-    <t>Proportion of children aged 24-59 months who are developmentally on track in health, learning and psychosocial well-being, by sex</t>
+    <t>Proportion of children aged 24–59 months who are developmentally on track in health, learning and psychosocial well-being, by sex</t>
   </si>
   <si>
     <t>4.2</t>
@@ -574,7 +574,7 @@
     <t>5.3.1</t>
   </si>
   <si>
-    <t>Proportion of women aged 20-24 years who were married or in a union before age 15 and before age 18</t>
+    <t>Proportion of women aged 20–24 years who were married or in a union before age 15 and before age 18</t>
   </si>
   <si>
     <t>5.3</t>
@@ -583,7 +583,7 @@
     <t>5.3.2</t>
   </si>
   <si>
-    <t>Proportion of girls and women aged 15-49 years who have undergone female genital mutilation/cutting, by age</t>
+    <t>Proportion of girls and women aged 15–49 years who have undergone female genital mutilation/cutting, by age</t>
   </si>
   <si>
     <t>5.4.1</t>
@@ -613,7 +613,7 @@
     <t>5.6.1</t>
   </si>
   <si>
-    <t>Proportion of women aged 15-49 years who make their own informed decisions regarding sexual relations, contraceptive use and reproductive health care</t>
+    <t>Proportion of women aged 15–49 years who make their own informed decisions regarding sexual relations, contraceptive use and reproductive health care</t>
   </si>
   <si>
     <t>5.6</t>
@@ -859,7 +859,7 @@
     <t>8.6.1</t>
   </si>
   <si>
-    <t>Proportion of youth (aged 15-24 years) not in education, employment or training</t>
+    <t>Proportion of youth (aged 15–24 years) not in education, employment or training</t>
   </si>
   <si>
     <t>8.6</t>
@@ -868,7 +868,7 @@
     <t>8.7.1</t>
   </si>
   <si>
-    <t>Proportion and number of children aged 5-17 years engaged in child labour, by sex and age</t>
+    <t>Proportion and number of children aged 5–17 years engaged in child labour, by sex and age</t>
   </si>
   <si>
     <t>8.7</t>
@@ -1627,7 +1627,7 @@
     <t>16.2.1</t>
   </si>
   <si>
-    <t>Proportion of children aged 1-17 years who experienced any physical punishment and/or psychological aggression by caregivers in the past month</t>
+    <t>Proportion of children aged 1–17 years who experienced any physical punishment and/or psychological aggression by caregivers in the past month</t>
   </si>
   <si>
     <t>16.2</t>
@@ -1642,7 +1642,7 @@
     <t>16.2.3</t>
   </si>
   <si>
-    <t>Proportion of young women and men aged 18-29 years who experienced sexual violence by age 18</t>
+    <t>Proportion of young women and men aged 18–29 years who experienced sexual violence by age 18</t>
   </si>
   <si>
     <t>16.3.1</t>
@@ -1858,7 +1858,7 @@
     <t>17.9.1</t>
   </si>
   <si>
-    <t>Dollar value of financial and technical assistance (including through North-South, South-South and triangular cooperation) committed to developing countries</t>
+    <t>Dollar value of financial and technical assistance (including through North-South, South‑South and triangular cooperation) committed to developing countries</t>
   </si>
   <si>
     <t>17.9</t>
